--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-22) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-22) Legacy.xlsx
@@ -981,19 +981,19 @@
         <v>2181147677</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2181147677</v>
+        <v>2181861827</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2181147677</v>
+        <v>2181861827</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>714150</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>100</v>
+        <v>100.0327419370789</v>
       </c>
     </row>
     <row r="20">
